--- a/docs/collections/tanaka/metadata/data.xlsx
+++ b/docs/collections/tanaka/metadata/data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2597">
   <si>
     <t>タイトル</t>
   </si>
@@ -7503,6 +7503,309 @@
   </si>
   <si>
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b7b22418-218f-25b4-8a01-cd236420774f/manifest</t>
+  </si>
+  <si>
+    <t>博物學寫眞圖</t>
+  </si>
+  <si>
+    <t>ハクブツガク シャシンズ</t>
+  </si>
+  <si>
+    <t>田中房種録 ; 服部雪齋画「瑇瑁又玳瑁」を含む|写本|書名は題簽による|その他の画者: 伊藤熊太郎, 伊藤熊太郎, 松平康民|おもに図版、彩色あり、折り込み図あり|書簡, 押紙あり|版心下部に「農商務省」とある罫紙を使用|明治10年1月宮田六左衞門刻「瑇瑁又玳瑁」(1枚)を付す|大和綴じ|印記: 「中島」(中島仰山), 「伊藤」(伊藤熊太郎), 「高野」(高野則明), 「男爵田中美津男氏寄贈先代田中芳男男旧藏書/昭和七年」</t>
+  </si>
+  <si>
+    <t>A00:5839</t>
+  </si>
+  <si>
+    <t>田中芳男 [編] ; 中島仰山 [ほか] 冩</t>
+  </si>
+  <si>
+    <t>田中芳男 [ほか写]</t>
+  </si>
+  <si>
+    <t>明治11-明治19</t>
+  </si>
+  <si>
+    <t>日本語</t>
+  </si>
+  <si>
+    <t>図書</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/55ee833b-6708-1fb2-2aa0-158792fa0066.json</t>
+  </si>
+  <si>
+    <t>55ee833b-6708-1fb2-2aa0-158792fa0066</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/tanaka/document/55ee833b-6708-1fb2-2aa0-158792fa0066</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/448f000887c5b888afe16bd77bb4f26ba15e9227.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/738699</t>
+  </si>
+  <si>
+    <t>10000135</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/55ee833b-6708-1fb2-2aa0-158792fa0066/manifest</t>
+  </si>
+  <si>
+    <t>鳥類標本及寫眞圖</t>
+  </si>
+  <si>
+    <t>チョウルイ ヒョウホン オヨビ シャシンズ</t>
+  </si>
+  <si>
+    <t>写本|書名は背表紙による|おもに図版|彩色あり|羽毛標本実物あり|付箋あり|貼交帖|印記: 「中島」(中島仰山), 「男爵田中美津男氏寄贈先代田中芳男男旧藏書/昭和七年」</t>
+  </si>
+  <si>
+    <t>A00:5840</t>
+  </si>
+  <si>
+    <t>中島仰山 [圖]</t>
+  </si>
+  <si>
+    <t>中島仰山 [自筆]</t>
+  </si>
+  <si>
+    <t>[明治期]</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b5ac62ab-5854-536f-254c-3451a79f37af.json</t>
+  </si>
+  <si>
+    <t>b5ac62ab-5854-536f-254c-3451a79f37af</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/tanaka/document/b5ac62ab-5854-536f-254c-3451a79f37af</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/57a728d956af2f0d04974829b5f30a34bcdc8988.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/738698</t>
+  </si>
+  <si>
+    <t>10000136</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b5ac62ab-5854-536f-254c-3451a79f37af/manifest</t>
+  </si>
+  <si>
+    <t>蟲譜 3巻 [1]</t>
+  </si>
+  <si>
+    <t>チュウフ</t>
+  </si>
+  <si>
+    <t>写本|書名は原表紙による|中の扉書名: 虫類|後付題簽の書名: 丹洲蟲譜|原表紙に「雪齋藏夲」とあり|本文中に「文化丁丑仲夏近藤正齋秘弆医學舘薬品會所排列也」との記述あり|付箋に「此書は明治九年十月服部雪斎翁ノ贈ル所ニシテ十年三月表装ス 田中芳男」, 「前紙は服部雪齋藏中ヲ写シタルモノ又後紙葉は伊藤圭介氏ノ藏中を写シ増加ズ」とあり|四周双辺無界料紙を使用|彩色あり|付箋あり|印記: 「雪齋」(服部雪齋), 「男爵田中美津男氏寄贈先代田中芳男男旧藏書/昭和七年」</t>
+  </si>
+  <si>
+    <t>A00:5843</t>
+  </si>
+  <si>
+    <t>丹洲 [撰] ; 服部雪齋 [原画]</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>[書写者不明]</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4ded9e40-0e43-4d93-202d-ef954c646725.json</t>
+  </si>
+  <si>
+    <t>4ded9e40-0e43-4d93-202d-ef954c646725</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/tanaka/document/4ded9e40-0e43-4d93-202d-ef954c646725</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e3aaae38cad1c31093bc6e0ee2d659508ccf4a07.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/738697</t>
+  </si>
+  <si>
+    <t>10000137</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4ded9e40-0e43-4d93-202d-ef954c646725/manifest</t>
+  </si>
+  <si>
+    <t>蟲譜 3巻 [2]</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/19f5c39a-2be4-0356-0095-0a80224d0744.json</t>
+  </si>
+  <si>
+    <t>19f5c39a-2be4-0356-0095-0a80224d0744</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/tanaka/document/19f5c39a-2be4-0356-0095-0a80224d0744</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/dee165cf4c09cb89962b1b0a69a21f6b4fbe9e84.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/738696</t>
+  </si>
+  <si>
+    <t>10000138</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/19f5c39a-2be4-0356-0095-0a80224d0744/manifest</t>
+  </si>
+  <si>
+    <t>雀巣庵禽譜</t>
+  </si>
+  <si>
+    <t>ジャクソウアン キンプ</t>
+  </si>
+  <si>
+    <t>写本|書名は序首による|序に「本年五月水谷助六氏ノ周旋ニ因リ神波全庵君ヨリ求ムル啚書ノ内鳥圖ニ巻ハ尾張ノ本草家雀巣庵主人ノ遺物ナルヨシ甚内傳冩モアレトモ多クハ同翁ノ自筆ニ成レリ ... 明治十九年六月二十一日 東京田中芳男記」とあり|おもに図版|彩色あり|印記: 「神波」(神波全庵), 「男爵田中美津男氏寄贈先代田中芳男男旧藏書/昭和七年」</t>
+  </si>
+  <si>
+    <t>A00:5844</t>
+  </si>
+  <si>
+    <t>雀巣庵 [著] ; 田中芳男 [編]</t>
+  </si>
+  <si>
+    <t>吉田雀巣庵 : 田中芳男 [写]</t>
+  </si>
+  <si>
+    <t>[江戸後期]-明治19 識語</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b317c66e-9ca0-8325-9719-27ffecd40aee.json</t>
+  </si>
+  <si>
+    <t>b317c66e-9ca0-8325-9719-27ffecd40aee</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/tanaka/document/b317c66e-9ca0-8325-9719-27ffecd40aee</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/71c150ef4a712efd7f7154e97f7eba8b89b9585a.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/738695</t>
+  </si>
+  <si>
+    <t>10000139</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b317c66e-9ca0-8325-9719-27ffecd40aee/manifest</t>
+  </si>
+  <si>
+    <t>隨観冩真 20巻 (存4巻) [1]</t>
+  </si>
+  <si>
+    <t>ズイカン シャシン</t>
+  </si>
+  <si>
+    <t>写本|書名は目首による|扉の書名: 隨觀冩眞|責任表示は『日本古典籍総合目録データベース』による|題簽による巻冊次表示: 中(魚之部), 下(魚鱉蟹介之部)|おもに図版|彩色あり|印記: 「男爵田中美津男氏寄贈先代田中芳男男旧藏書/昭和七年」</t>
+  </si>
+  <si>
+    <t>A00:5845</t>
+  </si>
+  <si>
+    <t>[後藤梨春著]</t>
+  </si>
+  <si>
+    <t>[幕末明治期]</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/36dda72b-3eae-17a3-9ce0-84d1a3bd86c6.json</t>
+  </si>
+  <si>
+    <t>36dda72b-3eae-17a3-9ce0-84d1a3bd86c6</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/tanaka/document/36dda72b-3eae-17a3-9ce0-84d1a3bd86c6</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/839a39765cbe2afd2a1b4db973265a52e3318129.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/738694</t>
+  </si>
+  <si>
+    <t>10000140</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/36dda72b-3eae-17a3-9ce0-84d1a3bd86c6/manifest</t>
+  </si>
+  <si>
+    <t>隨観冩真 20巻 (存4巻) [2]</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/3fe00c71-9cc6-02f8-0bae-72a95b754874.json</t>
+  </si>
+  <si>
+    <t>3fe00c71-9cc6-02f8-0bae-72a95b754874</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/tanaka/document/3fe00c71-9cc6-02f8-0bae-72a95b754874</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d2f8d4e0a546972bdf09ca5d74a6633ee30f9bd0.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/738693</t>
+  </si>
+  <si>
+    <t>10000141</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/3fe00c71-9cc6-02f8-0bae-72a95b754874/manifest</t>
+  </si>
+  <si>
+    <t>蟲豸圖譜 (存2巻)</t>
+  </si>
+  <si>
+    <t>チュウチ ズフ</t>
+  </si>
+  <si>
+    <t>写本|題簽の書名: 蟲豸啚譜|田中芳男筆跡の題簽に「明治十九年博物局藏写本ヲ複写ス」とあり|彩色あり|印記: 「男爵田中美津男氏寄贈先代田中芳男男旧藏書/昭和七年」</t>
+  </si>
+  <si>
+    <t>A00:5847</t>
+  </si>
+  <si>
+    <t>[田中芳男模画]</t>
+  </si>
+  <si>
+    <t>[田中芳男] [写]</t>
+  </si>
+  <si>
+    <t>明治19</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9818d4b7-41d5-2ad8-4e02-e1ff9d7b1dd2.json</t>
+  </si>
+  <si>
+    <t>9818d4b7-41d5-2ad8-4e02-e1ff9d7b1dd2</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/tanaka/document/9818d4b7-41d5-2ad8-4e02-e1ff9d7b1dd2</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4fef220db87fde61365fe8c6d0897e66693be218.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/738692</t>
+  </si>
+  <si>
+    <t>10000142</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9818d4b7-41d5-2ad8-4e02-e1ff9d7b1dd2/manifest</t>
   </si>
 </sst>
 </file>
@@ -7838,7 +8141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI237"/>
+  <dimension ref="A1:AI245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:35">
@@ -8052,7 +8355,7 @@
         <v>67</v>
       </c>
       <c r="AI2" t="n">
-        <v>29964</v>
+        <v>30879</v>
       </c>
     </row>
     <row r="3" spans="1:35">
@@ -25552,6 +25855,670 @@
         <v>241</v>
       </c>
     </row>
+    <row r="238" spans="1:35">
+      <c r="A238" t="s">
+        <v>2496</v>
+      </c>
+      <c r="B238" t="s">
+        <v>2497</v>
+      </c>
+      <c r="C238" t="s"/>
+      <c r="D238" t="s"/>
+      <c r="E238" t="s">
+        <v>2498</v>
+      </c>
+      <c r="F238" t="s"/>
+      <c r="G238" t="s"/>
+      <c r="H238" t="s">
+        <v>2499</v>
+      </c>
+      <c r="I238" t="s">
+        <v>2500</v>
+      </c>
+      <c r="J238" t="s"/>
+      <c r="K238" t="s">
+        <v>2363</v>
+      </c>
+      <c r="L238" t="s"/>
+      <c r="M238" t="s">
+        <v>2501</v>
+      </c>
+      <c r="N238" t="s">
+        <v>2502</v>
+      </c>
+      <c r="O238" t="s">
+        <v>2503</v>
+      </c>
+      <c r="P238" t="s">
+        <v>2504</v>
+      </c>
+      <c r="Q238" t="s">
+        <v>2505</v>
+      </c>
+      <c r="R238" t="s">
+        <v>2506</v>
+      </c>
+      <c r="S238" t="s">
+        <v>1260</v>
+      </c>
+      <c r="T238" t="s">
+        <v>2507</v>
+      </c>
+      <c r="U238" t="s">
+        <v>79</v>
+      </c>
+      <c r="V238" t="s">
+        <v>2508</v>
+      </c>
+      <c r="W238" t="s">
+        <v>2509</v>
+      </c>
+      <c r="X238" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y238" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z238" t="s"/>
+      <c r="AA238" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB238" t="s">
+        <v>2510</v>
+      </c>
+      <c r="AC238" t="s"/>
+      <c r="AD238" t="s">
+        <v>2511</v>
+      </c>
+      <c r="AE238" t="s"/>
+      <c r="AF238" t="s"/>
+      <c r="AG238" t="s"/>
+      <c r="AH238" t="s"/>
+      <c r="AI238" t="n">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="239" spans="1:35">
+      <c r="A239" t="s">
+        <v>2512</v>
+      </c>
+      <c r="B239" t="s">
+        <v>2513</v>
+      </c>
+      <c r="C239" t="s"/>
+      <c r="D239" t="s"/>
+      <c r="E239" t="s">
+        <v>2514</v>
+      </c>
+      <c r="F239" t="s"/>
+      <c r="G239" t="s"/>
+      <c r="H239" t="s">
+        <v>2515</v>
+      </c>
+      <c r="I239" t="s">
+        <v>2516</v>
+      </c>
+      <c r="J239" t="s"/>
+      <c r="K239" t="s">
+        <v>2363</v>
+      </c>
+      <c r="L239" t="s"/>
+      <c r="M239" t="s">
+        <v>2517</v>
+      </c>
+      <c r="N239" t="s">
+        <v>2518</v>
+      </c>
+      <c r="O239" t="s">
+        <v>2503</v>
+      </c>
+      <c r="P239" t="s">
+        <v>2504</v>
+      </c>
+      <c r="Q239" t="s">
+        <v>2519</v>
+      </c>
+      <c r="R239" t="s">
+        <v>2520</v>
+      </c>
+      <c r="S239" t="s">
+        <v>1260</v>
+      </c>
+      <c r="T239" t="s">
+        <v>2521</v>
+      </c>
+      <c r="U239" t="s">
+        <v>79</v>
+      </c>
+      <c r="V239" t="s">
+        <v>2522</v>
+      </c>
+      <c r="W239" t="s">
+        <v>2523</v>
+      </c>
+      <c r="X239" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y239" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z239" t="s"/>
+      <c r="AA239" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB239" t="s">
+        <v>2524</v>
+      </c>
+      <c r="AC239" t="s"/>
+      <c r="AD239" t="s">
+        <v>2525</v>
+      </c>
+      <c r="AE239" t="s"/>
+      <c r="AF239" t="s"/>
+      <c r="AG239" t="s"/>
+      <c r="AH239" t="s"/>
+      <c r="AI239" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="240" spans="1:35">
+      <c r="A240" t="s">
+        <v>2526</v>
+      </c>
+      <c r="B240" t="s">
+        <v>2527</v>
+      </c>
+      <c r="C240" t="s"/>
+      <c r="D240" t="s"/>
+      <c r="E240" t="s">
+        <v>2528</v>
+      </c>
+      <c r="F240" t="s"/>
+      <c r="G240" t="s"/>
+      <c r="H240" t="s">
+        <v>2529</v>
+      </c>
+      <c r="I240" t="s">
+        <v>2530</v>
+      </c>
+      <c r="J240" t="s"/>
+      <c r="K240" t="s">
+        <v>2531</v>
+      </c>
+      <c r="L240" t="s"/>
+      <c r="M240" t="s">
+        <v>2532</v>
+      </c>
+      <c r="N240" t="s">
+        <v>2518</v>
+      </c>
+      <c r="O240" t="s">
+        <v>2503</v>
+      </c>
+      <c r="P240" t="s">
+        <v>2504</v>
+      </c>
+      <c r="Q240" t="s">
+        <v>2533</v>
+      </c>
+      <c r="R240" t="s">
+        <v>2534</v>
+      </c>
+      <c r="S240" t="s">
+        <v>1260</v>
+      </c>
+      <c r="T240" t="s">
+        <v>2535</v>
+      </c>
+      <c r="U240" t="s">
+        <v>79</v>
+      </c>
+      <c r="V240" t="s">
+        <v>2536</v>
+      </c>
+      <c r="W240" t="s">
+        <v>2537</v>
+      </c>
+      <c r="X240" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y240" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z240" t="s"/>
+      <c r="AA240" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB240" t="s">
+        <v>2538</v>
+      </c>
+      <c r="AC240" t="s"/>
+      <c r="AD240" t="s">
+        <v>2539</v>
+      </c>
+      <c r="AE240" t="s"/>
+      <c r="AF240" t="s"/>
+      <c r="AG240" t="s"/>
+      <c r="AH240" t="s"/>
+      <c r="AI240" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="241" spans="1:35">
+      <c r="A241" t="s">
+        <v>2540</v>
+      </c>
+      <c r="B241" t="s">
+        <v>2527</v>
+      </c>
+      <c r="C241" t="s"/>
+      <c r="D241" t="s"/>
+      <c r="E241" t="s">
+        <v>2528</v>
+      </c>
+      <c r="F241" t="s"/>
+      <c r="G241" t="s"/>
+      <c r="H241" t="s">
+        <v>2529</v>
+      </c>
+      <c r="I241" t="s">
+        <v>2530</v>
+      </c>
+      <c r="J241" t="s"/>
+      <c r="K241" t="s">
+        <v>2531</v>
+      </c>
+      <c r="L241" t="s"/>
+      <c r="M241" t="s">
+        <v>2532</v>
+      </c>
+      <c r="N241" t="s">
+        <v>2518</v>
+      </c>
+      <c r="O241" t="s">
+        <v>2503</v>
+      </c>
+      <c r="P241" t="s">
+        <v>2504</v>
+      </c>
+      <c r="Q241" t="s">
+        <v>2541</v>
+      </c>
+      <c r="R241" t="s">
+        <v>2542</v>
+      </c>
+      <c r="S241" t="s">
+        <v>1260</v>
+      </c>
+      <c r="T241" t="s">
+        <v>2543</v>
+      </c>
+      <c r="U241" t="s">
+        <v>79</v>
+      </c>
+      <c r="V241" t="s">
+        <v>2544</v>
+      </c>
+      <c r="W241" t="s">
+        <v>2545</v>
+      </c>
+      <c r="X241" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y241" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z241" t="s"/>
+      <c r="AA241" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB241" t="s">
+        <v>2546</v>
+      </c>
+      <c r="AC241" t="s"/>
+      <c r="AD241" t="s">
+        <v>2547</v>
+      </c>
+      <c r="AE241" t="s"/>
+      <c r="AF241" t="s"/>
+      <c r="AG241" t="s"/>
+      <c r="AH241" t="s"/>
+      <c r="AI241" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="242" spans="1:35">
+      <c r="A242" t="s">
+        <v>2548</v>
+      </c>
+      <c r="B242" t="s">
+        <v>2549</v>
+      </c>
+      <c r="C242" t="s"/>
+      <c r="D242" t="s"/>
+      <c r="E242" t="s">
+        <v>2550</v>
+      </c>
+      <c r="F242" t="s"/>
+      <c r="G242" t="s"/>
+      <c r="H242" t="s">
+        <v>2551</v>
+      </c>
+      <c r="I242" t="s">
+        <v>2552</v>
+      </c>
+      <c r="J242" t="s"/>
+      <c r="K242" t="s">
+        <v>2363</v>
+      </c>
+      <c r="L242" t="s"/>
+      <c r="M242" t="s">
+        <v>2553</v>
+      </c>
+      <c r="N242" t="s">
+        <v>2554</v>
+      </c>
+      <c r="O242" t="s">
+        <v>2503</v>
+      </c>
+      <c r="P242" t="s">
+        <v>2504</v>
+      </c>
+      <c r="Q242" t="s">
+        <v>2555</v>
+      </c>
+      <c r="R242" t="s">
+        <v>2556</v>
+      </c>
+      <c r="S242" t="s">
+        <v>1260</v>
+      </c>
+      <c r="T242" t="s">
+        <v>2557</v>
+      </c>
+      <c r="U242" t="s">
+        <v>79</v>
+      </c>
+      <c r="V242" t="s">
+        <v>2558</v>
+      </c>
+      <c r="W242" t="s">
+        <v>2559</v>
+      </c>
+      <c r="X242" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y242" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z242" t="s"/>
+      <c r="AA242" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB242" t="s">
+        <v>2560</v>
+      </c>
+      <c r="AC242" t="s"/>
+      <c r="AD242" t="s">
+        <v>2561</v>
+      </c>
+      <c r="AE242" t="s"/>
+      <c r="AF242" t="s"/>
+      <c r="AG242" t="s"/>
+      <c r="AH242" t="s"/>
+      <c r="AI242" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="243" spans="1:35">
+      <c r="A243" t="s">
+        <v>2562</v>
+      </c>
+      <c r="B243" t="s">
+        <v>2563</v>
+      </c>
+      <c r="C243" t="s"/>
+      <c r="D243" t="s"/>
+      <c r="E243" t="s">
+        <v>2564</v>
+      </c>
+      <c r="F243" t="s"/>
+      <c r="G243" t="s"/>
+      <c r="H243" t="s">
+        <v>2565</v>
+      </c>
+      <c r="I243" t="s">
+        <v>2566</v>
+      </c>
+      <c r="J243" t="s"/>
+      <c r="K243" t="s">
+        <v>2531</v>
+      </c>
+      <c r="L243" t="s"/>
+      <c r="M243" t="s">
+        <v>2532</v>
+      </c>
+      <c r="N243" t="s">
+        <v>2567</v>
+      </c>
+      <c r="O243" t="s">
+        <v>2503</v>
+      </c>
+      <c r="P243" t="s">
+        <v>2504</v>
+      </c>
+      <c r="Q243" t="s">
+        <v>2568</v>
+      </c>
+      <c r="R243" t="s">
+        <v>2569</v>
+      </c>
+      <c r="S243" t="s">
+        <v>1260</v>
+      </c>
+      <c r="T243" t="s">
+        <v>2570</v>
+      </c>
+      <c r="U243" t="s">
+        <v>79</v>
+      </c>
+      <c r="V243" t="s">
+        <v>2571</v>
+      </c>
+      <c r="W243" t="s">
+        <v>2572</v>
+      </c>
+      <c r="X243" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y243" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z243" t="s"/>
+      <c r="AA243" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB243" t="s">
+        <v>2573</v>
+      </c>
+      <c r="AC243" t="s"/>
+      <c r="AD243" t="s">
+        <v>2574</v>
+      </c>
+      <c r="AE243" t="s"/>
+      <c r="AF243" t="s"/>
+      <c r="AG243" t="s"/>
+      <c r="AH243" t="s"/>
+      <c r="AI243" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="244" spans="1:35">
+      <c r="A244" t="s">
+        <v>2575</v>
+      </c>
+      <c r="B244" t="s">
+        <v>2563</v>
+      </c>
+      <c r="C244" t="s"/>
+      <c r="D244" t="s"/>
+      <c r="E244" t="s">
+        <v>2564</v>
+      </c>
+      <c r="F244" t="s"/>
+      <c r="G244" t="s"/>
+      <c r="H244" t="s">
+        <v>2565</v>
+      </c>
+      <c r="I244" t="s">
+        <v>2566</v>
+      </c>
+      <c r="J244" t="s"/>
+      <c r="K244" t="s">
+        <v>2531</v>
+      </c>
+      <c r="L244" t="s"/>
+      <c r="M244" t="s">
+        <v>2532</v>
+      </c>
+      <c r="N244" t="s">
+        <v>2567</v>
+      </c>
+      <c r="O244" t="s">
+        <v>2503</v>
+      </c>
+      <c r="P244" t="s">
+        <v>2504</v>
+      </c>
+      <c r="Q244" t="s">
+        <v>2576</v>
+      </c>
+      <c r="R244" t="s">
+        <v>2577</v>
+      </c>
+      <c r="S244" t="s">
+        <v>1260</v>
+      </c>
+      <c r="T244" t="s">
+        <v>2578</v>
+      </c>
+      <c r="U244" t="s">
+        <v>79</v>
+      </c>
+      <c r="V244" t="s">
+        <v>2579</v>
+      </c>
+      <c r="W244" t="s">
+        <v>2580</v>
+      </c>
+      <c r="X244" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y244" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z244" t="s"/>
+      <c r="AA244" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB244" t="s">
+        <v>2581</v>
+      </c>
+      <c r="AC244" t="s"/>
+      <c r="AD244" t="s">
+        <v>2582</v>
+      </c>
+      <c r="AE244" t="s"/>
+      <c r="AF244" t="s"/>
+      <c r="AG244" t="s"/>
+      <c r="AH244" t="s"/>
+      <c r="AI244" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="245" spans="1:35">
+      <c r="A245" t="s">
+        <v>2583</v>
+      </c>
+      <c r="B245" t="s">
+        <v>2584</v>
+      </c>
+      <c r="C245" t="s"/>
+      <c r="D245" t="s"/>
+      <c r="E245" t="s">
+        <v>2585</v>
+      </c>
+      <c r="F245" t="s"/>
+      <c r="G245" t="s"/>
+      <c r="H245" t="s">
+        <v>2586</v>
+      </c>
+      <c r="I245" t="s">
+        <v>2587</v>
+      </c>
+      <c r="J245" t="s"/>
+      <c r="K245" t="s">
+        <v>2363</v>
+      </c>
+      <c r="L245" t="s"/>
+      <c r="M245" t="s">
+        <v>2588</v>
+      </c>
+      <c r="N245" t="s">
+        <v>2589</v>
+      </c>
+      <c r="O245" t="s">
+        <v>2503</v>
+      </c>
+      <c r="P245" t="s">
+        <v>2504</v>
+      </c>
+      <c r="Q245" t="s">
+        <v>2590</v>
+      </c>
+      <c r="R245" t="s">
+        <v>2591</v>
+      </c>
+      <c r="S245" t="s">
+        <v>1260</v>
+      </c>
+      <c r="T245" t="s">
+        <v>2592</v>
+      </c>
+      <c r="U245" t="s">
+        <v>79</v>
+      </c>
+      <c r="V245" t="s">
+        <v>2593</v>
+      </c>
+      <c r="W245" t="s">
+        <v>2594</v>
+      </c>
+      <c r="X245" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y245" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z245" t="s"/>
+      <c r="AA245" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB245" t="s">
+        <v>2595</v>
+      </c>
+      <c r="AC245" t="s"/>
+      <c r="AD245" t="s">
+        <v>2596</v>
+      </c>
+      <c r="AE245" t="s"/>
+      <c r="AF245" t="s"/>
+      <c r="AG245" t="s"/>
+      <c r="AH245" t="s"/>
+      <c r="AI245" t="n">
+        <v>57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
